--- a/figures/MNIST/tables/window_size/noise_0.5_delta_0.0/results.xlsx
+++ b/figures/MNIST/tables/window_size/noise_0.5_delta_0.0/results.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maciek\Documents\GitHub\MUNDataStream\figures\MNIST\tables\window_size\noise_0.5_delta_0.0\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF4D8154-EAF2-4730-9C5A-B57918C33D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="4650" yWindow="5730" windowWidth="28800" windowHeight="15885" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="accuracy" sheetId="1" r:id="rId1"/>
     <sheet name="recovery_time" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>window_size</t>
   </si>
@@ -35,17 +41,14 @@
     <t>accuracy_recovery_time</t>
   </si>
   <si>
-    <t>mean_memory</t>
-  </si>
-  <si>
     <t>mean_time</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,17 +107,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Pakiet Office 2007–2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -152,7 +163,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Pakiet Office 2007–2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -186,6 +197,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -220,9 +232,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Pakiet Office 2007–2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -395,11 +408,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -413,186 +426,186 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.8606687898089171</v>
+        <v>0.86066878980891715</v>
       </c>
       <c r="C2">
-        <v>0.7664102564102565</v>
+        <v>0.76641025641025651</v>
       </c>
       <c r="D2">
-        <v>0.9537341772151898</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>0.95373417721518983</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.8745594479830149</v>
+        <v>0.87455944798301488</v>
       </c>
       <c r="C3">
-        <v>0.7926923076923076</v>
+        <v>0.79269230769230759</v>
       </c>
       <c r="D3">
-        <v>0.9553902953586497</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>0.95539029535864972</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>6</v>
       </c>
       <c r="B4">
-        <v>0.8862579617834395</v>
+        <v>0.88625796178343952</v>
       </c>
       <c r="C4">
-        <v>0.8147970085470085</v>
+        <v>0.81479700854700854</v>
       </c>
       <c r="D4">
-        <v>0.9568143459915611</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>0.95681434599156112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.8939225053078557</v>
+        <v>0.89392250530785566</v>
       </c>
       <c r="C5">
-        <v>0.8294444444444444</v>
+        <v>0.82944444444444443</v>
       </c>
       <c r="D5">
-        <v>0.9575843881856541</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>0.95758438818565406</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>8</v>
       </c>
       <c r="B6">
-        <v>0.9023726114649682</v>
+        <v>0.90237261146496817</v>
       </c>
       <c r="C6">
-        <v>0.846068376068376</v>
+        <v>0.84606837606837604</v>
       </c>
       <c r="D6">
-        <v>0.957964135021097</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>0.95796413502109701</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9</v>
       </c>
       <c r="B7">
-        <v>0.9090286624203822</v>
+        <v>0.90902866242038216</v>
       </c>
       <c r="C7">
-        <v>0.855</v>
+        <v>0.85499999999999998</v>
       </c>
       <c r="D7">
-        <v>0.962373417721519</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>0.96237341772151896</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>10</v>
       </c>
       <c r="B8">
-        <v>0.9147505307855626</v>
+        <v>0.91475053078556257</v>
       </c>
       <c r="C8">
-        <v>0.8671794871794872</v>
+        <v>0.86717948717948723</v>
       </c>
       <c r="D8">
         <v>0.9617194092827005</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>11</v>
       </c>
       <c r="B9">
-        <v>0.9157165605095542</v>
+        <v>0.91571656050955419</v>
       </c>
       <c r="C9">
-        <v>0.8677457264957266</v>
+        <v>0.86774572649572657</v>
       </c>
       <c r="D9">
-        <v>0.9630801687763713</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>0.96308016877637126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>12</v>
       </c>
       <c r="B10">
-        <v>0.9175053078556263</v>
+        <v>0.91750530785562634</v>
       </c>
       <c r="C10">
         <v>0.871826923076923</v>
       </c>
       <c r="D10">
-        <v>0.9626054852320675</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>0.96260548523206746</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>13</v>
       </c>
       <c r="B11">
-        <v>0.9219108280254777</v>
+        <v>0.92191082802547775</v>
       </c>
       <c r="C11">
-        <v>0.8800641025641026</v>
+        <v>0.88006410256410261</v>
       </c>
       <c r="D11">
-        <v>0.9632278481012658</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>0.96322784810126583</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>14</v>
       </c>
       <c r="B12">
-        <v>0.9231104033970277</v>
+        <v>0.92311040339702766</v>
       </c>
       <c r="C12">
-        <v>0.8814743589743589</v>
+        <v>0.88147435897435888</v>
       </c>
       <c r="D12">
-        <v>0.9642194092827003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>0.96421940928270033</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>15</v>
       </c>
       <c r="B13">
-        <v>0.9217409766454352</v>
+        <v>0.92174097664543519</v>
       </c>
       <c r="C13">
-        <v>0.8798076923076923</v>
+        <v>0.87980769230769229</v>
       </c>
       <c r="D13">
-        <v>0.9631434599156118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>0.96314345991561179</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
       <c r="B14">
-        <v>0.8155148619957538</v>
+        <v>0.81551486199575385</v>
       </c>
       <c r="C14">
-        <v>0.7378952991452993</v>
+        <v>0.73789529914529928</v>
       </c>
       <c r="D14">
-        <v>0.8921518987341772</v>
+        <v>0.89215189873417722</v>
       </c>
     </row>
   </sheetData>
@@ -601,11 +614,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -615,11 +628,8 @@
       <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4</v>
       </c>
@@ -627,13 +637,10 @@
         <v>1.333333333333333</v>
       </c>
       <c r="C2">
-        <v>2497611.464968153</v>
-      </c>
-      <c r="D2">
-        <v>3.749038089267511</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>3.7490380892675108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>5</v>
       </c>
@@ -641,13 +648,10 @@
         <v>1.666666666666667</v>
       </c>
       <c r="C3">
-        <v>3117019.108280255</v>
-      </c>
-      <c r="D3">
-        <v>3.692293342399137</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>3.6922933423991369</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>6</v>
       </c>
@@ -655,13 +659,10 @@
         <v>1.333333333333333</v>
       </c>
       <c r="C4">
-        <v>3734428.662420382</v>
-      </c>
-      <c r="D4">
-        <v>3.680972747881126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>3.6809727478811261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>7</v>
       </c>
@@ -669,13 +670,10 @@
         <v>1.333333333333333</v>
       </c>
       <c r="C5">
-        <v>4349840.127388535</v>
-      </c>
-      <c r="D5">
-        <v>3.703488241883236</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>3.7034882418832362</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>8</v>
       </c>
@@ -683,13 +681,10 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>4963253.503184713</v>
-      </c>
-      <c r="D6">
-        <v>3.682862706532904</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>3.6828627065329038</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9</v>
       </c>
@@ -697,13 +692,10 @@
         <v>1.333333333333333</v>
       </c>
       <c r="C7">
-        <v>5574668.789808917</v>
-      </c>
-      <c r="D7">
-        <v>3.63573480876112</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>3.6357348087611201</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>10</v>
       </c>
@@ -711,13 +703,10 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>6184085.987261146</v>
-      </c>
-      <c r="D8">
-        <v>3.659508669144374</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>3.6595086691443739</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>11</v>
       </c>
@@ -725,13 +714,10 @@
         <v>1</v>
       </c>
       <c r="C9">
-        <v>6791505.0955414</v>
-      </c>
-      <c r="D9">
-        <v>3.677563803335454</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>3.6775638033354539</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>12</v>
       </c>
@@ -739,13 +725,10 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>7396926.11464968</v>
-      </c>
-      <c r="D10">
         <v>3.593523932315275</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>13</v>
       </c>
@@ -753,13 +736,10 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>8000349.044585987</v>
-      </c>
-      <c r="D11">
-        <v>3.591193455025473</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>3.5911934550254729</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>14</v>
       </c>
@@ -767,13 +747,10 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>8601773.885350319</v>
-      </c>
-      <c r="D12">
-        <v>3.490237320276036</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>3.4902373202760359</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>15</v>
       </c>
@@ -781,13 +758,10 @@
         <v>1</v>
       </c>
       <c r="C13">
-        <v>9201200.636942675</v>
-      </c>
-      <c r="D13">
         <v>1.837409695489387</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -795,10 +769,7 @@
         <v>4</v>
       </c>
       <c r="C14">
-        <v>8601773.885350319</v>
-      </c>
-      <c r="D14">
-        <v>6.673721573100852</v>
+        <v>6.6737215731008517</v>
       </c>
     </row>
   </sheetData>
